--- a/Config/xlsx/Type.xlsx
+++ b/Config/xlsx/Type.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="34">
   <si>
     <t>种类</t>
   </si>
@@ -114,6 +114,21 @@
   </si>
   <si>
     <t>NextID</t>
+  </si>
+  <si>
+    <t>图片ID</t>
+  </si>
+  <si>
+    <t>CharacterID</t>
+  </si>
+  <si>
+    <t>CharacterData</t>
+  </si>
+  <si>
+    <t>图片路径</t>
+  </si>
+  <si>
+    <t>ImagePath</t>
   </si>
 </sst>
 </file>
@@ -1100,7 +1115,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="13.5" customWidth="1"/>
@@ -1109,7 +1124,7 @@
     <col min="5" max="5" width="11.1333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="16.5" spans="1:9">
+    <row r="1" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1138,7 +1153,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" ht="16.5" spans="1:9">
+    <row r="2" ht="16.5" spans="1:11">
       <c r="A2" s="3" t="s">
         <v>9</v>
       </c>
@@ -1160,7 +1175,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" ht="16.5" spans="1:9">
+    <row r="3" ht="16.5" spans="1:11">
       <c r="A3" s="3" t="s">
         <v>9</v>
       </c>
@@ -1180,7 +1195,7 @@
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
     </row>
-    <row r="4" ht="16.5" spans="1:9">
+    <row r="4" ht="16.5" spans="1:11">
       <c r="A4" s="3" t="s">
         <v>9</v>
       </c>
@@ -1200,7 +1215,7 @@
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
     </row>
-    <row r="5" ht="16.5" spans="1:9">
+    <row r="5" ht="16.5" spans="1:11">
       <c r="A5" s="3" t="s">
         <v>9</v>
       </c>
@@ -1222,7 +1237,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" ht="16.5" spans="1:9">
+    <row r="6" ht="16.5" spans="1:11">
       <c r="A6" s="3" t="s">
         <v>9</v>
       </c>
@@ -1242,7 +1257,7 @@
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
     </row>
-    <row r="7" ht="16.5" spans="1:9">
+    <row r="7" ht="16.5" spans="1:11">
       <c r="A7" s="3" t="s">
         <v>9</v>
       </c>
@@ -1260,7 +1275,7 @@
       </c>
       <c r="F7" s="3"/>
     </row>
-    <row r="8" ht="16.5" spans="1:9">
+    <row r="8" ht="16.5" spans="1:11">
       <c r="A8" s="3" t="s">
         <v>9</v>
       </c>
@@ -1280,7 +1295,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" ht="16.5" spans="1:9">
+    <row r="9" ht="16.5" spans="1:11">
       <c r="A9" s="3" t="s">
         <v>9</v>
       </c>
@@ -1297,6 +1312,77 @@
         <v>13</v>
       </c>
       <c r="F9" s="3"/>
+    </row>
+    <row r="10" ht="16.5" spans="1:11">
+      <c r="A10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
+    </row>
+    <row r="11" ht="16.5" spans="1:11">
+      <c r="A11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3"/>
+    </row>
+    <row r="12" ht="16.5" spans="1:11">
+      <c r="A12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555556" footer="0.511805555555556"/>
